--- a/data/Parasites-db-Ida.xlsx
+++ b/data/Parasites-db-Ida.xlsx
@@ -475,12 +475,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>small intestine</t>
+          <t>skin, lung, small intestine</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>BTO:0000651</t>
+          <t>BTO:0001253, BTO:0000763, BTO:0000651</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rattus norvegicus</t>
+          <t>Rattus norvegicus, Mus musculus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rattus norvegicus</t>
+          <t>Rattus norvegicus, Mus musculus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -595,12 +595,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>lymph vessel, blood</t>
+          <t>lymph vessel, lymph node, blood</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BTO:0000752, BTO:0000089</t>
+          <t>BTO:0000752, BTO:0000784, BTO:0000089</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -635,12 +635,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>lymph vessel, blood</t>
+          <t>lymph vessel, lymph node, blood</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BTO:0000752, BTO:0000089</t>
+          <t>BTO:0000752, BTO:0000784, BTO:0000089</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Homo sapiens</t>
+          <t>Homo sapiens, Rattus norvegicus, Mus musculus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -783,12 +783,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>stomach, skin</t>
+          <t>small intestine, skin</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BTO:0001307, BTO:0001253</t>
+          <t>BTO:0000651, BTO:0001253</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -935,12 +935,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>colon</t>
+          <t>colon, skin</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BTO:0000269</t>
+          <t>BTO:0000269, BTO:0001253</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rattus norvegicus, Homo sapiens</t>
+          <t>Homo sapiens, Rattus norvegicus, Mus musculus</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rattus norvegicus</t>
+          <t>Rattus norvegicus, Mus musculus</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1127,12 +1127,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Liver, spleen, bone marrow, skin, blood</t>
+          <t>Liver, spleen, bone marrow, lymph node, skin, blood, macrophage</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>BTO:0000759, BTO:0001281, BTO:0000141, BTO:0001253, BTO:0000089</t>
+          <t>BTO:0000759, BTO:0001281, BTO:0000141, BTO:0000784, BTO:0001253, BTO:0000089, BTO:0000801</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Skin, blood, nose, mouth</t>
+          <t>Skin, blood, macrophage</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>BTO:0001253, BTO:0000089, BTO:0000840, BTO:0001090</t>
+          <t>BTO:0001253, BTO:0000089, BTO:0000801</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1191,12 +1191,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Skin, blood, lung, eye</t>
+          <t>Skin, blood, eye</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>BTO:0001253, BTO:0000089, BTO:0000763, BTO:0000439</t>
+          <t>BTO:0001253, BTO:0000089, BTO:0000439</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1231,12 +1231,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>small intestine</t>
+          <t>skin, lung, small intestine</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>BTO:0000651</t>
+          <t>BTO:0001253, BTO:0000763, BTO:0000651</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Skin</t>
+          <t>Skin, eye</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>BTO:0001253</t>
+          <t>BTO:0001253, BTO:0000439</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1379,12 +1379,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Skin, liver, blood</t>
+          <t>Skin, liver, blood, brain, spleen</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>BTO:0001253, BTO:0000759, BTO:0000089</t>
+          <t>BTO:0001253, BTO:0000759, BTO:0000089, BTO:0000142, BTO:0001281</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Skin, liver, small intestine, blood</t>
+          <t>Skin, liver, small intestine, lung, blood</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>BTO:0001253, BTO:0000759, BTO:0000651, BTO:0000089</t>
+          <t>BTO:0001253, BTO:0000759, BTO:0000651, BTO:0000763, BTO:0000089</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1571,12 +1571,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Skin, liver, intestine, lung, blood</t>
+          <t>Skin, liver, intestine, spleen, lung, blood</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>BTO:0001253, BTO:0000759, BTO:0000648, BTO:0000763, BTO:0000089</t>
+          <t>BTO:0001253, BTO:0000759, BTO:0000648, BTO:0001281, BTO:0000763, BTO:0000089</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>small intestine</t>
+          <t>skin, lung, small intestine</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>BTO:0000651</t>
+          <t>BTO:0001253, BTO:0000763, BTO:0000651</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Blood,brain,eye,heart,muscle, placenta</t>
+          <t>Blood, brain, eye, heart, muscle, placenta, lymph node</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>BTO:0000089, BTO:0000142, BTO:0000439, BTO:0000562, BTO:0000887, BTO:0001078</t>
+          <t>BTO:0000089, BTO:0000142, BTO:0000439, BTO:0000562, BTO:0000887, BTO:0001078, BTO:0000784</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Intestine, muscle</t>
+          <t>Intestine, muscle, brain, heart, lung</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>BTO:0000648, BTO:0000887</t>
+          <t>BTO:0000648, BTO:0000887, BTO:0000142, BTO:0000562, BTO:0000763</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Intestine, muscle</t>
+          <t>Intestine, muscle, brain, heart, lung</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>BTO:0000648, BTO:0000887</t>
+          <t>BTO:0000648, BTO:0000887, BTO:0000142, BTO:0000562, BTO:0000763</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Intestine, muscle</t>
+          <t>Intestine, muscle, brain, heart, lung</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>BTO:0000648, BTO:0000887</t>
+          <t>BTO:0000648, BTO:0000887, BTO:0000142, BTO:0000562, BTO:0000763</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sus scrofa</t>
+          <t>Homo sapiens, Sus scrofa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sus scrofa</t>
+          <t>Homo sapiens, Sus scrofa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2043,12 +2043,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>small intestine, colon</t>
+          <t>colon</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>BTO:0000651, BTO:0000269</t>
+          <t>BTO:0000269</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Skin, heart, blood, eye</t>
+          <t>Skin, heart, colon, muscle, blood, eye</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>BTO:0001253, BTO:0000562, BTO:0000089, BTO:0000439</t>
+          <t>BTO:0001253, BTO:0000562, BTO:0000269, BTO:0000887, BTO:0000089, BTO:0000439</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2234,7 +2234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4510,6 +4510,1510 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Onchocerca volvulus</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>tissue</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Skin</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Skin, eye</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>biology</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>onchocerciasis is river blindness; the eye was missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Onchocerca volvulus</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>BTO_id</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>BTO:0001253</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>BTO:0001253, BTO:0000439</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>biology</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>onchocerciasis is river blindness; the eye was missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Leishmania major</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>tissue</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Skin, blood, nose, mouth</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Skin, blood, macrophage</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>biology</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>mucosal disease is a Viannia trait (L. braziliensis); L. major is Old World cutaneous, so nose and mouth removed. Macrophage added for consistency across Leishmania</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Leishmania major</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>BTO_id</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>BTO:0001253, BTO:0000089, BTO:0000840, BTO:0001090</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>BTO:0001253, BTO:0000089, BTO:0000801</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>biology</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>mucosal disease is a Viannia trait (L. braziliensis); L. major is Old World cutaneous, so nose and mouth removed. Macrophage added for consistency across Leishmania</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Trichuris trichiura</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>tissue</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>small intestine, colon</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>colon</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>biology</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>whipworm attaches in the caecum and ascending colon, not the small intestine</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Trichuris trichiura</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>BTO_id</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>BTO:0000651, BTO:0000269</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>BTO:0000269</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>biology</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>whipworm attaches in the caecum and ascending colon, not the small intestine</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Plasmodium falciparum</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>tissue</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Skin, liver, blood</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Skin, liver, blood, brain, spleen</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>biology</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>cerebral malaria is the defining severe manifestation and separates P. falciparum from P. vivax and P. knowlesi</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Plasmodium falciparum</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>BTO_id</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>BTO:0001253, BTO:0000759, BTO:0000089</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>BTO:0001253, BTO:0000759, BTO:0000089, BTO:0000142, BTO:0001281</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>biology</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>cerebral malaria is the defining severe manifestation and separates P. falciparum from P. vivax and P. knowlesi</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Ancylostoma ceylanicum</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>tissue</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>small intestine</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>skin, lung, small intestine</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>consistency</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>larval skin-lung migration, recorded the same way as for Schistosoma and Plasmodium</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Ancylostoma ceylanicum</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>BTO_id</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>BTO:0000651</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>BTO:0001253, BTO:0000763, BTO:0000651</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>consistency</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>larval skin-lung migration, recorded the same way as for Schistosoma and Plasmodium</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Necator americanus</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>tissue</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>small intestine</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>skin, lung, small intestine</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>consistency</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>larval skin-lung migration, recorded the same way as for Schistosoma and Plasmodium</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Necator americanus</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>BTO_id</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>BTO:0000651</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>BTO:0001253, BTO:0000763, BTO:0000651</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>consistency</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>larval skin-lung migration, recorded the same way as for Schistosoma and Plasmodium</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Strongyloides stercoralis</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>tissue</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>small intestine</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>skin, lung, small intestine</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>consistency</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>larval skin-lung migration and autoinfection</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Strongyloides stercoralis</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>BTO_id</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>BTO:0000651</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>BTO:0001253, BTO:0000763, BTO:0000651</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>consistency</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>larval skin-lung migration and autoinfection</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Brugia malayi</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>tissue</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>lymph vessel, blood</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>lymph vessel, lymph node, blood</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>consistency</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>lymph node, as already recorded for Wuchereria bancrofti</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Brugia malayi</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>BTO_id</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>BTO:0000752, BTO:0000089</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>BTO:0000752, BTO:0000784, BTO:0000089</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>consistency</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>lymph node, as already recorded for Wuchereria bancrofti</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Brugia timori</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>tissue</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>lymph vessel, blood</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>lymph vessel, lymph node, blood</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>consistency</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>lymph node, as already recorded for Wuchereria bancrofti</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Brugia timori</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>BTO_id</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>BTO:0000752, BTO:0000089</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>BTO:0000752, BTO:0000784, BTO:0000089</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>consistency</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>lymph node, as already recorded for Wuchereria bancrofti</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Trichinella britovi</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>tissue</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Intestine, muscle</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Intestine, muscle, brain, heart, lung</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>consistency</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>myocarditis and encephalitis are trichinellosis complications generally, already recorded for T. spiralis and T. pseudospiralis</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Trichinella britovi</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>BTO_id</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>BTO:0000648, BTO:0000887</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>BTO:0000648, BTO:0000887, BTO:0000142, BTO:0000562, BTO:0000763</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>consistency</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>myocarditis and encephalitis are trichinellosis complications generally, already recorded for T. spiralis and T. pseudospiralis</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Trichinella nativa</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>tissue</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Intestine, muscle</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Intestine, muscle, brain, heart, lung</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>consistency</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>myocarditis and encephalitis are trichinellosis complications generally, already recorded for T. spiralis and T. pseudospiralis</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Trichinella nativa</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>BTO_id</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>BTO:0000648, BTO:0000887</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>BTO:0000648, BTO:0000887, BTO:0000142, BTO:0000562, BTO:0000763</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>consistency</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>myocarditis and encephalitis are trichinellosis complications generally, already recorded for T. spiralis and T. pseudospiralis</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Trichinella nelsoni</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>tissue</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Intestine, muscle</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Intestine, muscle, brain, heart, lung</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>consistency</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>myocarditis and encephalitis are trichinellosis complications generally, already recorded for T. spiralis and T. pseudospiralis</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Trichinella nelsoni</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>BTO_id</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>BTO:0000648, BTO:0000887</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>BTO:0000648, BTO:0000887, BTO:0000142, BTO:0000562, BTO:0000763</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>consistency</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>myocarditis and encephalitis are trichinellosis complications generally, already recorded for T. spiralis and T. pseudospiralis</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Schistosoma japonicum</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>tissue</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Skin, liver, small intestine, blood</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Skin, liver, small intestine, lung, blood</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>consistency</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>lung stage of the migration, as recorded for S. mansoni and S. haematobium</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Schistosoma japonicum</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>BTO_id</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>BTO:0001253, BTO:0000759, BTO:0000651, BTO:0000089</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>BTO:0001253, BTO:0000759, BTO:0000651, BTO:0000763, BTO:0000089</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>consistency</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>lung stage of the migration, as recorded for S. mansoni and S. haematobium</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Trypanosoma cruzi</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>tissue</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Skin, heart, blood, eye</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Skin, heart, colon, muscle, blood, eye</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>biology</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>chronic Chagas disease: megacolon and myositis alongside the cardiomyopathy</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Trypanosoma cruzi</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>BTO_id</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>BTO:0001253, BTO:0000562, BTO:0000089, BTO:0000439</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>BTO:0001253, BTO:0000562, BTO:0000269, BTO:0000887, BTO:0000089, BTO:0000439</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>biology</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>chronic Chagas disease: megacolon and myositis alongside the cardiomyopathy</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Leishmania infantum</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>tissue</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Liver, spleen, bone marrow, skin, blood</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Liver, spleen, bone marrow, lymph node, skin, blood, macrophage</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>biology</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>lymphadenopathy in visceral leishmaniasis; macrophage added for consistency across Leishmania</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Leishmania infantum</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>BTO_id</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>BTO:0000759, BTO:0001281, BTO:0000141, BTO:0001253, BTO:0000089</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>BTO:0000759, BTO:0001281, BTO:0000141, BTO:0000784, BTO:0001253, BTO:0000089, BTO:0000801</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>biology</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>lymphadenopathy in visceral leishmaniasis; macrophage added for consistency across Leishmania</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Toxoplasma gondii</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>tissue</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Blood,brain,eye,heart,muscle, placenta</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Blood, brain, eye, heart, muscle, placenta, lymph node</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>biology</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>lymphadenopathy is the commonest presentation of acute toxoplasmosis</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Toxoplasma gondii</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>BTO_id</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>BTO:0000089, BTO:0000142, BTO:0000439, BTO:0000562, BTO:0000887, BTO:0001078</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>BTO:0000089, BTO:0000142, BTO:0000439, BTO:0000562, BTO:0000887, BTO:0001078, BTO:0000784</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>biology</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>lymphadenopathy is the commonest presentation of acute toxoplasmosis</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Schistosoma mansoni</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>tissue</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Skin, liver, intestine, lung, blood</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Skin, liver, intestine, spleen, lung, blood</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>biology</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>hepatosplenic schistosomiasis</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Schistosoma mansoni</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>BTO_id</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>BTO:0001253, BTO:0000759, BTO:0000648, BTO:0000763, BTO:0000089</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>BTO:0001253, BTO:0000759, BTO:0000648, BTO:0001281, BTO:0000763, BTO:0000089</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>biology</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>hepatosplenic schistosomiasis</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Enterobius vermicularis</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>tissue</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>colon</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>colon, skin</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>biology</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>eggs are deposited on perianal skin, which is the main symptom</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Enterobius vermicularis</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>BTO_id</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>BTO:0000269</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>BTO:0000269, BTO:0001253</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>biology</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>eggs are deposited on perianal skin, which is the main symptom</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Dracunculus medinensis</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>tissue</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>stomach, skin</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>small intestine, skin</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>biology</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>larvae penetrate the duodenal wall rather than the stomach, as the row's own comment says</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Dracunculus medinensis</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>BTO_id</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>BTO:0001307, BTO:0001253</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>BTO:0000651, BTO:0001253</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>biology</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>larvae penetrate the duodenal wall rather than the stomach, as the row's own comment says</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Loa loa</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>tissue</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Skin, blood, lung, eye</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Skin, blood, eye</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>biology</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>loiasis is subcutaneous migration with subconjunctival passage; pulmonary involvement is rare</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Loa loa</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>BTO_id</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>BTO:0001253, BTO:0000089, BTO:0000763, BTO:0000439</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>BTO:0001253, BTO:0000089, BTO:0000439</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>biology</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>loiasis is subcutaneous migration with subconjunctival passage; pulmonary involvement is rare</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Cryptosporidium muris</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Homo sapiens, Rattus norvegicus, Mus musculus</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>principally a rodent gastric parasite, and also a documented if uncommon human pathogen, so all three hosts are recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Trichinella spiralis</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Sus scrofa</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Homo sapiens, Sus scrofa</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>pigs are the domestic reservoir and humans are infected via pork; Sus scrofa also keeps the pig proteome in use</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Trichinella pseudospiralis</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Sus scrofa</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Homo sapiens, Sus scrofa</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>pigs are the domestic reservoir and humans are infected via pork; Sus scrofa also keeps the pig proteome in use</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Hymenolepis diminuta</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Rattus norvegicus, Homo sapiens</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Homo sapiens, Rattus norvegicus, Mus musculus</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>mouse recorded explicitly; it was previously only implied by a note in config.yml, which is now removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Angiostrongylus cantonensis</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Rattus norvegicus</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Rattus norvegicus, Mus musculus</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>mouse recorded explicitly; it was previously only implied by a note in config.yml, which is now removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Angiostrongylus costaricensis</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Rattus norvegicus</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Rattus norvegicus, Mus musculus</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>mouse recorded explicitly; it was previously only implied by a note in config.yml, which is now removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Leishmania braziliensis</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Rattus norvegicus</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Rattus norvegicus, Mus musculus</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>mouse recorded explicitly; it was previously only implied by a note in config.yml, which is now removed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Parasites-db-Ida.xlsx
+++ b/data/Parasites-db-Ida.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="changes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="changes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,25 +435,30 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>intracellular/extracellular</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>tissue</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>BTO_id</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>host</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>comments</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
@@ -475,25 +480,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Extracellular</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>skin, lung, small intestine</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>BTO:0001253, BTO:0000763, BTO:0000651</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Among the zoonotic hookworms, A. ceylanicum is the only one capable of maturing and reproducing in humans</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>(Tenorio et al., 2024), (Hawdon &amp; Wise, 2021)</t>
         </is>
@@ -515,25 +525,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Extracellular</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>lung, brain</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>BTO:0000763, BTO:0000142</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Rattus norvegicus, Mus musculus</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Rodents from the genus g. Rattus, with some main ones being Rattus norvegicus and Rattus rattus.</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>(Griffin et al., 2025)</t>
         </is>
@@ -555,25 +570,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>Extracellular</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>mesenteric artery, blood</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>BTO:0000779, BTO:0000089</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Rattus norvegicus, Mus musculus</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>(Sigmodon hispidus, Rattus rattus), terrestrial mollusks (Sarasinula plebeia) as intermediate hosts and humans are accidental hosts</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>(Rojas et al., 2021)</t>
         </is>
@@ -595,25 +615,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>Extracellular</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>lymph vessel, lymph node, blood</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>BTO:0000752, BTO:0000784, BTO:0000089</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>As a final host or mammalians (monkey and cats)</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>CDC, (Diekmann et al., 2025), (Junsiri et al., 2024)</t>
         </is>
@@ -635,25 +660,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>Extracellular</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>lymph vessel, lymph node, blood</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>BTO:0000752, BTO:0000784, BTO:0000089</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Parasitic filarial nematodes require both an intermediate vector (mosquito) host and a definitive (mammalian) host to complete their life cycle.</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>(Kulpa et al., 2023)</t>
         </is>
@@ -675,21 +705,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>Extracellular</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>liver, bile duct</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>BTO:0000759, BTO:0000122</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>(Na et al., 2020)</t>
         </is>
@@ -711,21 +745,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>Intracellular</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>stomach, intestine</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>BTO:0001307, BTO:0000648</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Homo sapiens, Rattus norvegicus, Mus musculus</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>(Wang et al., 2021), CDC</t>
         </is>
@@ -747,25 +785,29 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>Intracellular</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>small intestine</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>BTO:0000651</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Infects the brush border of the small intestine, mainly the ileum. Taxid 353152 is the Iowa II reference isolate used by STRING</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -783,25 +825,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>Extracellular</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>small intestine, skin</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>BTO:0000651, BTO:0001253</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Intestinal wall</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>(Chaudhury, 2022), CDC</t>
         </is>
@@ -823,25 +870,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>Extracellular</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>liver, lung</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>BTO:0000759, BTO:0000763</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>humans are aberrant intermediate hosts, liver and lungs, spleen, kidneys, heart, bone, and central nervous system, including the brain and eyes</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>CDC., (Woolsey &amp; Miller, 2021)</t>
         </is>
@@ -863,21 +915,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>Extracellular</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>liver, lung</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>BTO:0000759, BTO:0000763</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>CDC., (Woolsey &amp; Miller, 2021)</t>
         </is>
@@ -899,21 +955,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>Extracellular</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>colon, liver, brain, lung</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>BTO:0000269, BTO:0000759, BTO:0000142, BTO:0000763</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>CDC.</t>
         </is>
@@ -935,21 +995,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>Extracellular</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>colon, skin</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>BTO:0000269, BTO:0001253</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>CDC</t>
         </is>
@@ -971,25 +1035,29 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>Extracellular</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>small intestine</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>BTO:0000651</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Trophozoites attach to the duodenal and jejunal mucosa. Giardia lamblia, G. intestinalis and G. duodenalis are the same organism (NCBI species 5741); taxid 184922 is the assemblage A reference isolate used by STRING</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1007,25 +1075,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>Extracellular</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>small intestine</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>BTO:0000651</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Homo sapiens, Rattus norvegicus, Mus musculus</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>humans can accidentally enter into the life cycle of this tapeworm via the ingestion of infected insects. Rodent definitive hosts include Rattus norvegicus and R. rattus</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>CDC., (Panti-May et al., 2020)</t>
         </is>
@@ -1033,51 +1106,56 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>6945</v>
+        <v>5660</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ixodes scapularis</t>
+          <t>Leishmania braziliensis</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Multicellular</t>
+          <t>Unicellular</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Skin</t>
+          <t>Intracellular</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BTO:0001253</t>
+          <t>Skin, nose, mouth, macrophage, blood</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Homo sapiens</t>
+          <t>BTO:0001253, BTO:0000840, BTO:0001090, BTO:0000801, BTO:0000089</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Humans are incidental hosts of I. scapularis and its associated pathogens. Three-host tick: larvae and nymphs feed on small rodents and passerine birds, adults feed on large mammals (white-tailed deer, humans)</t>
+          <t>Rattus norvegicus, Mus musculus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nelder et al., 2016)., (Eisen &amp; Eisen, 2018)., CDC</t>
+          <t>These parasites have a heteroxenous life cycle, with vertebrate mammalian hosts (humans, dogs, Rodents, canids, marsupials and primates) and an invertebrate vector insect</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>(Diniz et al., 2014)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>5660</v>
+        <v>5671</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Leishmania braziliensis</t>
+          <t>Leishmania infantum</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1087,37 +1165,32 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Skin, nose, mouth, macrophage, blood</t>
+          <t>Intracellular</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>BTO:0001253, BTO:0000840, BTO:0001090, BTO:0000801, BTO:0000089</t>
+          <t>Liver, spleen, bone marrow, lymph node, skin, blood, macrophage</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rattus norvegicus, Mus musculus</t>
+          <t>BTO:0000759, BTO:0001281, BTO:0000141, BTO:0000784, BTO:0001253, BTO:0000089, BTO:0000801</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>These parasites have a heteroxenous life cycle, with vertebrate mammalian hosts (humans, dogs, Rodents, canids, marsupials and primates) and an invertebrate vector insect</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Diniz et al., 2014)</t>
+          <t>Homo sapiens</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>5671</v>
+        <v>5664</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Leishmania infantum</t>
+          <t>Leishmania major</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1127,61 +1200,77 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Liver, spleen, bone marrow, lymph node, skin, blood, macrophage</t>
+          <t>Intracellular</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>BTO:0000759, BTO:0001281, BTO:0000141, BTO:0000784, BTO:0001253, BTO:0000089, BTO:0000801</t>
+          <t>Skin, blood, macrophage</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>BTO:0001253, BTO:0000089, BTO:0000801</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>5664</v>
+        <v>7209</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Leishmania major</t>
+          <t>Loa loa</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Unicellular</t>
+          <t>Multicellular</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Skin, blood, macrophage</t>
+          <t>Extracellular</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>BTO:0001253, BTO:0000089, BTO:0000801</t>
+          <t>Skin, blood, eye</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>BTO:0001253, BTO:0000089, BTO:0000439</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Vector: Chrysops species. Of all the simian hosts, Mandrillus leucophaeus has been found to have the highest prevalence (96%) of simian loiasis</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>(Chunda et al., 2023)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>7209</v>
+        <v>51031</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Loa loa</t>
+          <t>Necator americanus</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1191,37 +1280,37 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Skin, blood, eye</t>
+          <t>Extracellular</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>BTO:0001253, BTO:0000089, BTO:0000439</t>
+          <t>skin, lung, small intestine</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>BTO:0001253, BTO:0000763, BTO:0000651</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Vector: Chrysops species. Of all the simian hosts, Mandrillus leucophaeus has been found to have the highest prevalence (96%) of simian loiasis</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Chunda et al., 2023)</t>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>CDC</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>51031</v>
+        <v>6282</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Necator americanus</t>
+          <t>Onchocerca volvulus</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1231,33 +1320,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>skin, lung, small intestine</t>
+          <t>Extracellular</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>BTO:0001253, BTO:0000763, BTO:0000651</t>
+          <t>Skin, eye</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>BTO:0001253, BTO:0000439</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>CDC</t>
+          <t>Vector: blackfly(genusSimulium)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>CDC, (Lustigman et al., 2018)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>6282</v>
+        <v>147828</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Onchocerca volvulus</t>
+          <t>Opisthorchis felineus</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1267,37 +1365,37 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Skin, eye</t>
+          <t>Extracellular</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>BTO:0001253, BTO:0000439</t>
+          <t>Liver, bile duct, small intestine</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>BTO:0000759, BTO:0000122, BTO:0000651</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Vector: blackfly(genusSimulium)</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>CDC, (Lustigman et al., 2018)</t>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>(Pakharukova &amp; Mordvinov, 2016)., CDC</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>147828</v>
+        <v>6198</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Opisthorchis felineus</t>
+          <t>Opisthorchis viverrini</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1307,69 +1405,77 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Liver, bile duct, small intestine</t>
+          <t>Extracellular</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>BTO:0000759, BTO:0000122, BTO:0000651</t>
+          <t>Liver, bile duct</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>BTO:0000759, BTO:0000122</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Pakharukova &amp; Mordvinov, 2016)., CDC</t>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>(Sripa et al., 2025)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>6198</v>
+        <v>36329</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Opisthorchis viverrini</t>
+          <t>Plasmodium falciparum</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Multicellular</t>
+          <t>Unicellular</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Liver, bile duct</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>BTO:0000759, BTO:0000122</t>
+          <t>Skin, liver, blood, brain, spleen</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>BTO:0001253, BTO:0000759, BTO:0000089, BTO:0000142, BTO:0001281</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Sripa et al., 2025)</t>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>CDC</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>36329</v>
+        <v>5851</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Plasmodium falciparum</t>
+          <t>Plasmodium knowlesi</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1379,33 +1485,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Skin, liver, blood, brain, spleen</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>BTO:0001253, BTO:0000759, BTO:0000089, BTO:0000142, BTO:0001281</t>
+          <t>Skin, liver, blood</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>BTO:0001253, BTO:0000759, BTO:0000089</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>CDC</t>
+          <t>macaques as natural host</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>(Singh &amp; Daneshvar, 2013), (White, 2008)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>5851</v>
+        <v>126793</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Plasmodium knowlesi</t>
+          <t>Plasmodium vivax</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1415,61 +1530,70 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>Skin, liver, blood</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>BTO:0001253, BTO:0000759, BTO:0000089</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>macaques as natural host</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Singh &amp; Daneshvar, 2013), (White, 2008)</t>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>CDC</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126793</v>
+        <v>6185</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Plasmodium vivax</t>
+          <t>Schistosoma haematobium</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Unicellular</t>
+          <t>Multicellular</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Skin, liver, blood</t>
+          <t>Extracellular</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>BTO:0001253, BTO:0000759, BTO:0000089</t>
+          <t>Skin, urinary bladder, rectum, liver, blood, lung</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
+          <t>BTO:0001253, BTO:0001418, BTO:0001158, BTO:0000759, BTO:0000089, BTO:0000763</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
+        <is>
+          <t>Intermediate hosts are snails of the genera Bulinus</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>CDC</t>
         </is>
@@ -1477,11 +1601,11 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>6185</v>
+        <v>6182</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Schistosoma haematobium</t>
+          <t>Schistosoma japonicum</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1491,37 +1615,42 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Skin, urinary bladder, rectum, liver, blood, lung</t>
+          <t>Extracellular</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>BTO:0001253, BTO:0001418, BTO:0001158, BTO:0000759, BTO:0000089, BTO:0000763</t>
+          <t>Skin, liver, small intestine, lung, blood</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
+          <t>BTO:0001253, BTO:0000759, BTO:0000651, BTO:0000763, BTO:0000089</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Intermediate hosts are snails of the genera Bulinus</t>
-        </is>
-      </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>CDC</t>
+          <t>Intermediate hosts are snails of the genus Oncomelania</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>CDC, (Zhou et al., 2009)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>6182</v>
+        <v>6183</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Schistosoma japonicum</t>
+          <t>Schistosoma mansoni</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1531,37 +1660,42 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Skin, liver, small intestine, lung, blood</t>
+          <t>Extracellular</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>BTO:0001253, BTO:0000759, BTO:0000651, BTO:0000763, BTO:0000089</t>
+          <t>Skin, liver, intestine, spleen, lung, blood</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
+          <t>BTO:0001253, BTO:0000759, BTO:0000648, BTO:0001281, BTO:0000763, BTO:0000089</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Intermediate hosts are snails of the genus Oncomelania</t>
-        </is>
-      </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>CDC, (Zhou et al., 2009)</t>
+          <t>Intermediate hosts are snails of the genus Biomphalaria spp</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>CDC</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>6183</v>
+        <v>6248</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Schistosoma mansoni</t>
+          <t>Strongyloides stercoralis</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1571,37 +1705,37 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Skin, liver, intestine, spleen, lung, blood</t>
+          <t>Extracellular</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>BTO:0001253, BTO:0000759, BTO:0000648, BTO:0001281, BTO:0000763, BTO:0000089</t>
+          <t>skin, lung, small intestine</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
+          <t>BTO:0001253, BTO:0000763, BTO:0000651</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Intermediate hosts are snails of the genus Biomphalaria spp</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>CDC</t>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>CDC, (Czeresnia &amp; Weiss, 2022)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>6248</v>
+        <v>60517</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Strongyloides stercoralis</t>
+          <t>Taenia asiatica</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1611,33 +1745,42 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>skin, lung, small intestine</t>
+          <t>Extracellular</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>BTO:0001253, BTO:0000763, BTO:0000651</t>
+          <t>small intestine</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
+          <t>BTO:0000651</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>CDC, (Czeresnia &amp; Weiss, 2022)</t>
+          <t>pigs as intermediate host</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>(Parija, 2022)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>60517</v>
+        <v>6265</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Taenia asiatica</t>
+          <t>Toxocara canis</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1647,77 +1790,87 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>small intestine</t>
+          <t>Extracellular</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>BTO:0000651</t>
+          <t>liver, heart, lung, brain, muscle, eye</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
+          <t>BTO:0000759, BTO:0000562, BTO:0000763, BTO:0000142, BTO:0000887, BTO:0000439</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>pigs as intermediate host</t>
-        </is>
-      </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Parija, 2022)</t>
+          <t>humans are accidental hosts who become infected by ingesting infective eggs image or undercooked meat/viscera of infected paratenic hosts</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>CDC, (Schwartz et al., 2022)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>6265</v>
+        <v>432359</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Toxocara canis</t>
+          <t>Toxoplasma gondii</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Multicellular</t>
+          <t>Unicellular</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>liver, heart, lung, brain, muscle, eye</t>
+          <t>Intracellular</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>BTO:0000759, BTO:0000562, BTO:0000763, BTO:0000142, BTO:0000887, BTO:0000439</t>
+          <t>Blood, brain, eye, heart, muscle, placenta, lymph node</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
+          <t>BTO:0000089, BTO:0000142, BTO:0000439, BTO:0000562, BTO:0000887, BTO:0001078, BTO:0000784</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>humans are accidental hosts who become infected by ingesting infective eggs image or undercooked meat/viscera of infected paratenic hosts</t>
-        </is>
-      </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>CDC, (Schwartz et al., 2022)</t>
+          <t>T. gondii can naturally infect a wide range of warm-blooded intermediate hosts, ranging from birds to humans to rodents.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>CDC, (Kochanowsky &amp; Koshy, 2018)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>432359</v>
+        <v>72359</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Toxoplasma gondii</t>
+          <t>Trachipleistophora hominis</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1727,77 +1880,87 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Blood, brain, eye, heart, muscle, placenta, lymph node</t>
+          <t>Intracellular</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>BTO:0000089, BTO:0000142, BTO:0000439, BTO:0000562, BTO:0000887, BTO:0001078, BTO:0000784</t>
+          <t>Muscle, eye</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
+          <t>BTO:0000887, BTO:0000439</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>T. gondii can naturally infect a wide range of warm-blooded intermediate hosts, ranging from birds to humans to rodents.</t>
-        </is>
-      </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>CDC, (Kochanowsky &amp; Koshy, 2018)</t>
+          <t>natural host for T. hominis belongs to the hymenoptera.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>CDC, (Watson et al., 2015)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>72359</v>
+        <v>45882</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Trachipleistophora hominis</t>
+          <t>Trichinella britovi</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Unicellular</t>
+          <t>Multicellular</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Muscle, eye</t>
+          <t>Intracellular</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>BTO:0000887, BTO:0000439</t>
+          <t>Intestine, muscle, brain, heart, lung</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
+          <t>BTO:0000648, BTO:0000887, BTO:0000142, BTO:0000562, BTO:0000763</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>natural host for T. hominis belongs to the hymenoptera.</t>
-        </is>
-      </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>CDC, (Watson et al., 2015)</t>
+          <t>Most of the Homo sapiens cases occurring globally are due to pork consumption, carnivores of Europe and western Asia (Wild boar, red fox, raccoon dog</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>CDC, (Sharma et al., 2022)., (Pozio et al., 2009)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>45882</v>
+        <v>6335</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Trichinella britovi</t>
+          <t>Trichinella nativa</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1807,37 +1970,42 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>Intracellular</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>Intestine, muscle, brain, heart, lung</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>BTO:0000648, BTO:0000887, BTO:0000142, BTO:0000562, BTO:0000763</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Most of the Homo sapiens cases occurring globally are due to pork consumption, carnivores of Europe and western Asia (Wild boar, red fox, raccoon dog</t>
-        </is>
-      </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>CDC, (Sharma et al., 2022)., (Pozio et al., 2009)</t>
+          <t>polar bears, American mink, Arctic fox, Asian badger, badger, black bears, Wolverine (Gulo gulo)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>CDC, (Sharma et al., 2022), (Malone et al., 2025)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>6335</v>
+        <v>6336</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Trichinella nativa</t>
+          <t>Trichinella nelsoni</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1847,37 +2015,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t>Intracellular</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>Intestine, muscle, brain, heart, lung</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>BTO:0000648, BTO:0000887, BTO:0000142, BTO:0000562, BTO:0000763</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>polar bears, American mink, Arctic fox, Asian badger, badger, black bears, Wolverine (Gulo gulo)</t>
-        </is>
-      </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>CDC, (Sharma et al., 2022), (Malone et al., 2025)</t>
+          <t>Lion (Panthera leo), spotted hyena (Crocuta crocuta), leopard (Panthera pardus), cheetah (Actinonyx jubatus), bat-eared fox (Otocyon megalotis)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>CDC, (Mukaratirwa et al., 2013)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>6336</v>
+        <v>6337</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Trichinella nelsoni</t>
+          <t>Trichinella pseudospiralis</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1887,37 +2060,42 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t>Intracellular</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>Intestine, muscle, brain, heart, lung</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>BTO:0000648, BTO:0000887, BTO:0000142, BTO:0000562, BTO:0000763</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Homo sapiens</t>
-        </is>
-      </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lion (Panthera leo), spotted hyena (Crocuta crocuta), leopard (Panthera pardus), cheetah (Actinonyx jubatus), bat-eared fox (Otocyon megalotis)</t>
+          <t>Homo sapiens, Sus scrofa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>CDC, (Mukaratirwa et al., 2013)</t>
+          <t>mammals and birds worldwide, mountain lion (Puma concolor), wolverine, wild boars and 8 avian species 3 species of Accipitridae; 1 species of Cathartidae; 1 species of Corvidae; 1 species of Tytonidae; 2 species of Strigidae</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>(Pozio, 2016)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>6337</v>
+        <v>6334</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Trichinella pseudospiralis</t>
+          <t>Trichinella spiralis</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1927,149 +2105,167 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Intestine, muscle, brain, heart, lung</t>
+          <t>Intracellular</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>BTO:0000648, BTO:0000887, BTO:0000142, BTO:0000562, BTO:0000763</t>
+          <t>Intestine, brain, heart, muscle, lung</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
+          <t>BTO:0000648, BTO:0000142, BTO:0000562, BTO:0000887, BTO:0000763</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
           <t>Homo sapiens, Sus scrofa</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>mammals and birds worldwide, mountain lion (Puma concolor), wolverine, wild boars and 8 avian species 3 species of Accipitridae; 1 species of Cathartidae; 1 species of Corvidae; 1 species of Tytonidae; 2 species of Strigidae</t>
-        </is>
-      </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Pozio, 2016)</t>
+          <t>found worldwide in many carnivorous and omnivorous animals including humans, wild boars, Domestic pigs and brown rats (Rattus norvegicus)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>CDC, (Sharma et al., 2022), (Pozio &amp; Gomez Morales, 2023), (Pozio et al., 2009)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>6334</v>
+        <v>5722</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Trichinella spiralis</t>
+          <t>Trichomonas vaginalis</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Multicellular</t>
+          <t>Unicellular</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Intestine, brain, heart, muscle, lung</t>
+          <t>Extracellular</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>BTO:0000648, BTO:0000142, BTO:0000562, BTO:0000887, BTO:0000763</t>
+          <t>vagina, urethra</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Homo sapiens, Sus scrofa</t>
+          <t>BTO:0000243, BTO:0001426</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>found worldwide in many carnivorous and omnivorous animals including humans, wild boars, Domestic pigs and brown rats (Rattus norvegicus)</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>CDC, (Sharma et al., 2022), (Pozio &amp; Gomez Morales, 2023), (Pozio et al., 2009)</t>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>CDC, (Kissinger, 2015)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>5722</v>
+        <v>36087</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Trichomonas vaginalis</t>
+          <t>Trichuris trichiura</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Unicellular</t>
+          <t>Multicellular</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>vagina, urethra</t>
+          <t>Intracellular</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>BTO:0000243, BTO:0001426</t>
+          <t>colon</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
+          <t>BTO:0000269</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>CDC, (Kissinger, 2015)</t>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>CDC, (Izurieta et al., 2018)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>36087</v>
+        <v>185431</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Trichuris trichiura</t>
+          <t>Trypanosoma brucei</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Multicellular</t>
+          <t>Unicellular</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>colon</t>
+          <t>Extracellular</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>BTO:0000269</t>
+          <t>Skin, blood, brain, lymph node, spinal cord</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
+          <t>BTO:0001253, BTO:0000089, BTO:0000142, BTO:0000784, BTO:0001279</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>CDC, (Izurieta et al., 2018)</t>
+          <t>T. brucei brucei is not infectious to Homo sapiens but can cause disease in cattle, goats, and sheep (i.e., nagana), andtherefore contributes to the societal impact of these diseases.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>CDC, (Wang et al., 2008)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>185431</v>
+        <v>353153</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Trypanosoma brucei</t>
+          <t>Trypanosoma cruzi</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2079,37 +2275,42 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Skin, blood, brain, lymph node, spinal cord</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>BTO:0001253, BTO:0000089, BTO:0000142, BTO:0000784, BTO:0001279</t>
+          <t>Skin, heart, colon, muscle, blood, eye</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
+          <t>BTO:0001253, BTO:0000562, BTO:0000269, BTO:0000887, BTO:0000089, BTO:0000439</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>T. brucei brucei is not infectious to Homo sapiens but can cause disease in cattle, goats, and sheep (i.e., nagana), andtherefore contributes to the societal impact of these diseases.</t>
-        </is>
-      </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>CDC, (Wang et al., 2008)</t>
+          <t>humans, armadillos, opossums, raccoons, woodrats, some other rodents, and domestic dogs.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>CDC</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>353153</v>
+        <v>993615</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Trypanosoma cruzi</t>
+          <t>Vittaforma corneae</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2119,25 +2320,30 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Skin, heart, colon, muscle, blood, eye</t>
+          <t>Intracellular</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>BTO:0001253, BTO:0000562, BTO:0000269, BTO:0000887, BTO:0000089, BTO:0000439</t>
+          <t>eye</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
+          <t>BTO:0000439</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>humans, armadillos, opossums, raccoons, woodrats, some other rodents, and domestic dogs.</t>
-        </is>
-      </c>
       <c r="H45" t="inlineStr">
+        <is>
+          <t>No animal reservoir has been identified for Vittaforma cornea</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
         <is>
           <t>CDC</t>
         </is>
@@ -2145,79 +2351,44 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>993615</v>
+        <v>6293</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Vittaforma corneae</t>
+          <t>Wuchereria bancrofti</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Unicellular</t>
+          <t>Multicellular</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>eye</t>
+          <t>Extracellular</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>BTO:0000439</t>
+          <t>blood, lymph node, lymph vessel</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
+          <t>BTO:0000089, BTO:0000784, BTO:0000752</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>No animal reservoir has been identified for Vittaforma cornea</t>
-        </is>
-      </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>CDC</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>6293</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Wuchereria bancrofti</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Multicellular</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>blood, lymph node, lymph vessel</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>BTO:0000089, BTO:0000784, BTO:0000752</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Homo sapiens</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
           <t>Transmitted by many different mosquito some genera include: Aedes spp., Anopheles spp., Culex spp., Mansonia spp., and Coquillettida juxtamansonia.</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>CDC, (Small et al., 2019)</t>
         </is>
@@ -2234,7 +2405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F118"/>
+  <dimension ref="A1:F120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6014,6 +6185,70 @@
         </is>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Ixodes scapularis</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>(row)</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Ixodes scapularis</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>(removed)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>structure</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>ectoparasite: it feeds from outside the host and never enters it, so it is out of scope; already absent from config.yml</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>(all rows)</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>intracellular/extracellular</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>(absent)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Intracellular / Extracellular / Both</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>structure</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>where the parasite sits relative to the host cell, i.e. which host proteins it can reach. Distinct from unicelular/multicellular, which says which of the parasite's own proteins are exposed to the host. 'Both' is a life cycle with an intracellular and an extracellular stage in the same host (Plasmodium, T. cruzi)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Parasites-db-Ida.xlsx
+++ b/data/Parasites-db-Ida.xlsx
@@ -1445,7 +1445,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Intracellular</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Intracellular</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Intracellular</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Intracellular</t>
+          <t>Extracellular</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Intracellular</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2405,7 +2405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F120"/>
+  <dimension ref="A1:F122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6249,6 +6249,70 @@
         </is>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Plasmodium falciparum, P. knowlesi, P. vivax, Trypanosoma cruzi</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>intracellular/extracellular</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Intracellular</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>structure</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>the extracellular stages (sporozoites and merozoites, trypomastigotes) are transient non-replicative transit forms; the replicative niche in the host is inside a host cell, so the intracellular reach is the one that matters. Aligns with Parasites_db(3).xlsx, which does not use a Both category</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Trichuris trichiura</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>intracellular/extracellular</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Intracellular</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Extracellular</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>structure</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>the adult threads its anterior end through a syncytial tunnel in the intestinal epithelium but keeps its body in the lumen, so it is not enclosed in a host cell. Reserves Intracellular among the nematodes for Trichinella, whose larva sits wholly inside a single modified muscle cell (the nurse cell). Aligns with Parasites_db(3).xlsx</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
